--- a/workbooks/scenarios/HVACScenarios.xlsx
+++ b/workbooks/scenarios/HVACScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P104"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6884,6 +6884,126 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>I'm setting the thermostat for bedtime during a spring cold snap. What heat temperature is best for sleeping?</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" t="n">
+        <v>230</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>34</v>
+      </c>
+      <c r="I105" t="n">
+        <v>30</v>
+      </c>
+      <c r="J105" t="n">
+        <v>13</v>
+      </c>
+      <c r="K105" t="n">
+        <v>11</v>
+      </c>
+      <c r="L105" t="n">
+        <v>14</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>sleep</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>64</v>
+      </c>
+      <c r="O105" t="n">
+        <v>67</v>
+      </c>
+      <c r="P105" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>It's a very humid summer night and we're going to sleep. What AC temperature should I use?</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>York, PA</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>3</v>
+      </c>
+      <c r="F106" t="n">
+        <v>240</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>86</v>
+      </c>
+      <c r="I106" t="n">
+        <v>18</v>
+      </c>
+      <c r="J106" t="n">
+        <v>19</v>
+      </c>
+      <c r="K106" t="n">
+        <v>7</v>
+      </c>
+      <c r="L106" t="n">
+        <v>16</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>sleep</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>74</v>
+      </c>
+      <c r="O106" t="n">
+        <v>76</v>
+      </c>
+      <c r="P106" t="n">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workbooks/scenarios/HVACScenarios.xlsx
+++ b/workbooks/scenarios/HVACScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,82 +419,82 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>question</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Square Footage</t>
+          <t>square_footage</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Insulation</t>
+          <t>insulation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Household Size</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Utility Budget</t>
+          <t>utility_budget</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Housing Type</t>
+          <t>housing_type</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Outdoor Temp</t>
+          <t>outdoor_temp</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>House Age</t>
+          <t>house_age</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>R-Value</t>
+          <t>r_value</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>HVAC Age</t>
+          <t>hvac_age</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>seer</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Occupancy context</t>
+          <t>occupancy_context</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Alternative 1</t>
+          <t>alternative_1</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Alternative 2</t>
+          <t>alternative_2</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Alternative 3</t>
+          <t>alternative_3</t>
         </is>
       </c>
     </row>

--- a/workbooks/scenarios/HVACScenarios.xlsx
+++ b/workbooks/scenarios/HVACScenarios.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I'm working from home today with 1 person — what AC temperature should I set?</t>
+          <t>I'm working from home today with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I'm home all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm home all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 2 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what heat temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what AC temperature should I set?</t>
+          <t>I'm gone most of the day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I'm planning to stay in all day with 1 person — what AC temperature should I set?</t>
+          <t>I'm planning to stay in all day with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I'm around all day with 1 person — what heat temperature should I set?</t>
+          <t>I'm around all day with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I'm home for the day with 2 people — what AC temperature should I set?</t>
+          <t>I'm home for the day with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 2 people — what heat temperature should I set?</t>
+          <t>I'm spending the day at home with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I'm not planning to leave today with 2 people — what heat temperature should I set?</t>
+          <t>I'm not planning to leave today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1121,7 +1121,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I'm out of the house for a while — what AC temperature should I set?</t>
+          <t>I'm out of the house for a while, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1183,7 +1183,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I'm away most of today — what heat temperature should I set?</t>
+          <t>I'm away most of today, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I'm staying home today with 1 person — what AC temperature should I set?</t>
+          <t>I'm staying home today with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit — what AC temperature should I set for the rowhouse?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the rowhouse?</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1431,7 +1431,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the rowhouse?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the rowhouse?</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1493,7 +1493,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I'm not home today — what AC temperature should I set?</t>
+          <t>I'm not home today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I'm home and not going out with 5 people — what AC temperature should I set?</t>
+          <t>I'm home and not going out with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what AC temperature should I set for the townhouse?</t>
+          <t>I'm heading out for a quick errand, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I'm out for a couple hours — what heat temperature should I set for the townhouse?</t>
+          <t>I'm out for a couple hours, what heat temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I'm staying put today with 2 people — what heat temperature should I set?</t>
+          <t>I'm staying put today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>We're heading to bed soon — what heat temperature should I set overnight?</t>
+          <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>I'm working from home today with 4 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2547,7 +2547,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>I'm home all day with 5 people — what AC temperature should I set?</t>
+          <t>I'm home all day with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2609,7 +2609,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>I'm running out for a short while — what AC temperature should I set for the townhouse?</t>
+          <t>I'm running out for a short while, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2795,7 +2795,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>I'm gone for a few hours — what AC temperature should I set for the townhouse?</t>
+          <t>I'm gone for a few hours, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2919,7 +2919,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 3 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2981,7 +2981,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3043,7 +3043,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>I'm out of the house all day — what AC temperature should I set?</t>
+          <t>I'm out of the house all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3105,7 +3105,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3167,7 +3167,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit — what AC temperature should I set for the single-family?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the single-family?</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3229,7 +3229,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>I'm away for the day — what heat temperature should I set?</t>
+          <t>I'm away for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3415,7 +3415,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what AC temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3539,7 +3539,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>I'm planning to stay in all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm planning to stay in all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3663,7 +3663,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>I'm around all day with 3 people — what AC temperature should I set?</t>
+          <t>I'm around all day with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3787,7 +3787,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>I'm heading out and won't be back for hours — what AC temperature should I set?</t>
+          <t>I'm heading out and won't be back for hours, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3911,7 +3911,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>I'm home for the day with 2 people — what heat temperature should I set?</t>
+          <t>I'm home for the day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3973,7 +3973,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>I'm going to be out all day — what AC temperature should I set?</t>
+          <t>I'm going to be out all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4035,7 +4035,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>I'm leaving the house for most of the day — what AC temperature should I set?</t>
+          <t>I'm leaving the house for most of the day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4097,7 +4097,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4159,7 +4159,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>We're calling it a night — what heat temperature should I set overnight?</t>
+          <t>We're calling it a night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4221,7 +4221,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>We're about to turn in — what heat temperature should I set overnight?</t>
+          <t>We're about to turn in, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4345,7 +4345,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>We're heading to bed soon — what heat temperature should I set overnight?</t>
+          <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4407,7 +4407,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 3 people — what AC temperature should I set?</t>
+          <t>I'm spending the day at home with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4469,7 +4469,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>I'm not planning to leave today with 4 people — what AC temperature should I set?</t>
+          <t>I'm not planning to leave today with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4779,7 +4779,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>I'm staying home today with 2 people — what heat temperature should I set?</t>
+          <t>I'm staying home today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4903,7 +4903,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>I'm home and not going out with 4 people — what heat temperature should I set?</t>
+          <t>I'm home and not going out with 4 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4965,7 +4965,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the condo?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the condo?</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>I'm staying put today with 1 person — what heat temperature should I set?</t>
+          <t>I'm staying put today with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5151,7 +5151,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>I'm out of the house for a while — what AC temperature should I set?</t>
+          <t>I'm out of the house for a while, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5213,7 +5213,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5337,7 +5337,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>I'm working from home today with 2 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5399,7 +5399,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>I'm away most of today — what AC temperature should I set?</t>
+          <t>I'm away most of today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5523,7 +5523,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5585,7 +5585,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>I'm home all day with 4 people — what AC temperature should I set?</t>
+          <t>I'm home all day with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5647,7 +5647,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5709,7 +5709,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 5 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5771,7 +5771,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what heat temperature should I set for the single-family?</t>
+          <t>I'm heading out for a quick errand, what heat temperature should I set for the single-family?</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5833,7 +5833,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 1 person — what heat temperature should I set?</t>
+          <t>I'm sticking around the house with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5895,7 +5895,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>I'm gone for the entire workday — what heat temperature should I set?</t>
+          <t>I'm gone for the entire workday, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5957,7 +5957,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>I'm working from home today with 3 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6019,7 +6019,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6143,7 +6143,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>I'm staying in today with 3 people — what heat temperature should I set?</t>
+          <t>I'm staying in today with 3 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6267,7 +6267,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6329,7 +6329,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>I'm around all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm around all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6391,7 +6391,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>We're calling it a night — what heat temperature should I set overnight?</t>
+          <t>We're calling it a night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6453,7 +6453,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 3 people — what heat temperature should I set?</t>
+          <t>I'm not going anywhere with 3 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6515,7 +6515,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6639,7 +6639,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>I'm working from home today with 2 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6701,7 +6701,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6763,7 +6763,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what heat temperature should I set?</t>
+          <t>I'm gone most of the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6825,7 +6825,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">

--- a/workbooks/scenarios/HVACScenarios.xlsx
+++ b/workbooks/scenarios/HVACScenarios.xlsx
@@ -554,10 +554,8 @@
       <c r="O2" t="n">
         <v>76</v>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P2" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -616,10 +614,8 @@
       <c r="O3" t="n">
         <v>71</v>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="P3" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -678,10 +674,8 @@
       <c r="O4" t="n">
         <v>80</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="P4" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="5">
@@ -740,10 +734,8 @@
       <c r="O5" t="n">
         <v>68</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P5" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="6">
@@ -802,10 +794,8 @@
       <c r="O6" t="n">
         <v>77</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P6" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -864,10 +854,8 @@
       <c r="O7" t="n">
         <v>81</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P7" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -926,10 +914,8 @@
       <c r="O8" t="n">
         <v>67</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="P8" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -988,10 +974,8 @@
       <c r="O9" t="n">
         <v>79</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P9" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -1050,10 +1034,8 @@
       <c r="O10" t="n">
         <v>70</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="P10" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -1112,10 +1094,8 @@
       <c r="O11" t="n">
         <v>71</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="P11" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="12">
@@ -1174,10 +1154,8 @@
       <c r="O12" t="n">
         <v>79</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P12" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -1236,10 +1214,8 @@
       <c r="O13" t="n">
         <v>69</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P13" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -1298,10 +1274,8 @@
       <c r="O14" t="n">
         <v>79</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P14" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="15">
@@ -1360,10 +1334,8 @@
       <c r="O15" t="n">
         <v>76</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P15" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1422,10 +1394,8 @@
       <c r="O16" t="n">
         <v>81</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P16" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="17">
@@ -1484,10 +1454,8 @@
       <c r="O17" t="n">
         <v>68</v>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P17" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="18">
@@ -1546,10 +1514,8 @@
       <c r="O18" t="n">
         <v>78</v>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="P18" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -1608,10 +1574,8 @@
       <c r="O19" t="n">
         <v>81</v>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P19" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="20">
@@ -1670,10 +1634,8 @@
       <c r="O20" t="n">
         <v>75</v>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P20" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -1732,10 +1694,8 @@
       <c r="O21" t="n">
         <v>78</v>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="P21" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="22">
@@ -1794,10 +1754,8 @@
       <c r="O22" t="n">
         <v>69</v>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P22" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="23">
@@ -1856,10 +1814,8 @@
       <c r="O23" t="n">
         <v>68</v>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P23" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="24">
@@ -1918,10 +1874,8 @@
       <c r="O24" t="n">
         <v>78</v>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="P24" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="25">
@@ -1980,10 +1934,8 @@
       <c r="O25" t="n">
         <v>69</v>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P25" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="26">
@@ -2042,10 +1994,8 @@
       <c r="O26" t="n">
         <v>81</v>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P26" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="27">
@@ -2104,10 +2054,8 @@
       <c r="O27" t="n">
         <v>68</v>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P27" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="28">
@@ -2166,10 +2114,8 @@
       <c r="O28" t="n">
         <v>79</v>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P28" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="29">
@@ -2228,10 +2174,8 @@
       <c r="O29" t="n">
         <v>69</v>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P29" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="30">
@@ -2290,10 +2234,8 @@
       <c r="O30" t="n">
         <v>77</v>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P30" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="31">
@@ -2352,10 +2294,8 @@
       <c r="O31" t="n">
         <v>69</v>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P31" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="32">
@@ -2398,7 +2338,7 @@
         <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L32" t="n">
         <v>8</v>
@@ -2414,10 +2354,8 @@
       <c r="O32" t="n">
         <v>69</v>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P32" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="33">
@@ -2476,10 +2414,8 @@
       <c r="O33" t="n">
         <v>80</v>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P33" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="34">
@@ -2538,10 +2474,8 @@
       <c r="O34" t="n">
         <v>78</v>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P34" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="35">
@@ -2600,10 +2534,8 @@
       <c r="O35" t="n">
         <v>81</v>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="P35" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="36">
@@ -2662,10 +2594,8 @@
       <c r="O36" t="n">
         <v>79</v>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="P36" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="37">
@@ -2724,10 +2654,8 @@
       <c r="O37" t="n">
         <v>68</v>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P37" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="38">
@@ -2786,10 +2714,8 @@
       <c r="O38" t="n">
         <v>77</v>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="P38" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="39">
@@ -2848,10 +2774,8 @@
       <c r="O39" t="n">
         <v>76</v>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="P39" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="40">
@@ -2910,10 +2834,8 @@
       <c r="O40" t="n">
         <v>72</v>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P40" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="41">
@@ -2972,10 +2894,8 @@
       <c r="O41" t="n">
         <v>80</v>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P41" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="42">
@@ -3034,10 +2954,8 @@
       <c r="O42" t="n">
         <v>65</v>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="P42" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="43">
@@ -3096,10 +3014,8 @@
       <c r="O43" t="n">
         <v>81</v>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="P43" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="44">
@@ -3158,16 +3074,14 @@
       <c r="O44" t="n">
         <v>68</v>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="P44" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit, what AC temperature should I set for the single-family?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the single-family home?</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3220,10 +3134,8 @@
       <c r="O45" t="n">
         <v>80</v>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P45" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="46">
@@ -3282,10 +3194,8 @@
       <c r="O46" t="n">
         <v>63</v>
       </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="P46" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="47">
@@ -3344,10 +3254,8 @@
       <c r="O47" t="n">
         <v>76</v>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P47" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="48">
@@ -3406,10 +3314,8 @@
       <c r="O48" t="n">
         <v>78</v>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P48" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="49">
@@ -3468,10 +3374,8 @@
       <c r="O49" t="n">
         <v>77</v>
       </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P49" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="50">
@@ -3530,10 +3434,8 @@
       <c r="O50" t="n">
         <v>69</v>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P50" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="51">
@@ -3592,10 +3494,8 @@
       <c r="O51" t="n">
         <v>68</v>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P51" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="52">
@@ -3654,10 +3554,8 @@
       <c r="O52" t="n">
         <v>70</v>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="P52" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="53">
@@ -3716,10 +3614,8 @@
       <c r="O53" t="n">
         <v>76</v>
       </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P53" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="54">
@@ -3778,10 +3674,8 @@
       <c r="O54" t="n">
         <v>76</v>
       </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P54" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="55">
@@ -3840,10 +3734,8 @@
       <c r="O55" t="n">
         <v>77</v>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P55" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="56">
@@ -3902,10 +3794,8 @@
       <c r="O56" t="n">
         <v>68</v>
       </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="P56" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="57">
@@ -3964,10 +3854,8 @@
       <c r="O57" t="n">
         <v>70</v>
       </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="P57" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="58">
@@ -4150,10 +4038,8 @@
       <c r="O60" t="n">
         <v>77</v>
       </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P60" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="61">
@@ -4212,10 +4098,8 @@
       <c r="O61" t="n">
         <v>68</v>
       </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P61" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="62">
@@ -4274,10 +4158,8 @@
       <c r="O62" t="n">
         <v>70</v>
       </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="P62" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="63">
@@ -4336,10 +4218,8 @@
       <c r="O63" t="n">
         <v>70</v>
       </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="P63" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="64">
@@ -4398,10 +4278,8 @@
       <c r="O64" t="n">
         <v>69</v>
       </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="P64" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="65">
@@ -4460,10 +4338,8 @@
       <c r="O65" t="n">
         <v>77</v>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P65" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="66">
@@ -4522,10 +4398,8 @@
       <c r="O66" t="n">
         <v>68</v>
       </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P66" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="67">
@@ -4584,10 +4458,8 @@
       <c r="O67" t="n">
         <v>75</v>
       </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P67" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="68">
@@ -4646,10 +4518,8 @@
       <c r="O68" t="n">
         <v>68</v>
       </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="P68" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="69">
@@ -4708,10 +4578,8 @@
       <c r="O69" t="n">
         <v>78</v>
       </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P69" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="70">
@@ -4770,10 +4638,8 @@
       <c r="O70" t="n">
         <v>70</v>
       </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P70" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="71">
@@ -4832,10 +4698,8 @@
       <c r="O71" t="n">
         <v>69</v>
       </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P71" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="72">
@@ -4894,10 +4758,8 @@
       <c r="O72" t="n">
         <v>66</v>
       </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="P72" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="73">
@@ -4956,10 +4818,8 @@
       <c r="O73" t="n">
         <v>68</v>
       </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P73" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="74">
@@ -5018,10 +4878,8 @@
       <c r="O74" t="n">
         <v>66</v>
       </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="P74" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="75">
@@ -5080,10 +4938,8 @@
       <c r="O75" t="n">
         <v>68</v>
       </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="P75" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="76">
@@ -5142,10 +4998,8 @@
       <c r="O76" t="n">
         <v>72</v>
       </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="P76" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="77">
@@ -5204,10 +5058,8 @@
       <c r="O77" t="n">
         <v>72</v>
       </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="P77" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="78">
@@ -5266,10 +5118,8 @@
       <c r="O78" t="n">
         <v>68</v>
       </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P78" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="79">
@@ -5328,10 +5178,8 @@
       <c r="O79" t="n">
         <v>72</v>
       </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="P79" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="80">
@@ -5390,10 +5238,8 @@
       <c r="O80" t="n">
         <v>76</v>
       </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P80" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="81">
@@ -5452,10 +5298,8 @@
       <c r="O81" t="n">
         <v>80</v>
       </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="P81" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="82">
@@ -5514,10 +5358,8 @@
       <c r="O82" t="n">
         <v>77</v>
       </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="P82" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="83">
@@ -5576,10 +5418,8 @@
       <c r="O83" t="n">
         <v>81</v>
       </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P83" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="84">
@@ -5638,10 +5478,8 @@
       <c r="O84" t="n">
         <v>76</v>
       </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P84" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="85">
@@ -5700,10 +5538,8 @@
       <c r="O85" t="n">
         <v>81</v>
       </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P85" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="86">
@@ -5762,16 +5598,14 @@
       <c r="O86" t="n">
         <v>77</v>
       </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="P86" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand, what heat temperature should I set for the single-family?</t>
+          <t>I'm heading out for a quick errand, what heat temperature should I set for the single-family home?</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5824,10 +5658,8 @@
       <c r="O87" t="n">
         <v>66</v>
       </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="P87" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="88">
@@ -5886,10 +5718,8 @@
       <c r="O88" t="n">
         <v>69</v>
       </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P88" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="89">
@@ -5948,10 +5778,8 @@
       <c r="O89" t="n">
         <v>63</v>
       </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="P89" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="90">
@@ -6010,10 +5838,8 @@
       <c r="O90" t="n">
         <v>76</v>
       </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P90" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="91">
@@ -6072,10 +5898,8 @@
       <c r="O91" t="n">
         <v>63</v>
       </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="P91" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="92">
@@ -6134,10 +5958,8 @@
       <c r="O92" t="n">
         <v>79</v>
       </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P92" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="93">
@@ -6196,10 +6018,8 @@
       <c r="O93" t="n">
         <v>67</v>
       </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="P93" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="94">
@@ -6258,10 +6078,8 @@
       <c r="O94" t="n">
         <v>65</v>
       </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="P94" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="95">
@@ -6320,10 +6138,8 @@
       <c r="O95" t="n">
         <v>61</v>
       </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="P95" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="96">
@@ -6382,10 +6198,8 @@
       <c r="O96" t="n">
         <v>67</v>
       </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="P96" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="97">
@@ -6444,10 +6258,8 @@
       <c r="O97" t="n">
         <v>63</v>
       </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="P97" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="98">
@@ -6506,10 +6318,8 @@
       <c r="O98" t="n">
         <v>65</v>
       </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="P98" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="99">
@@ -6568,10 +6378,8 @@
       <c r="O99" t="n">
         <v>63</v>
       </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="P99" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="100">
@@ -6630,10 +6438,8 @@
       <c r="O100" t="n">
         <v>65</v>
       </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="P100" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="101">
@@ -6692,10 +6498,8 @@
       <c r="O101" t="n">
         <v>76</v>
       </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P101" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="102">
@@ -6754,10 +6558,8 @@
       <c r="O102" t="n">
         <v>81</v>
       </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P102" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="103">
@@ -6816,10 +6618,8 @@
       <c r="O103" t="n">
         <v>64</v>
       </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="P103" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="104">
@@ -6878,10 +6678,8 @@
       <c r="O104" t="n">
         <v>75</v>
       </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="P104" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="105">
